--- a/NEW BOT 02/Armature_Winding_Inventory_Movement.xlsx
+++ b/NEW BOT 02/Armature_Winding_Inventory_Movement.xlsx
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Production Module ⟶ Advance Production Reports ⟶ Inventory Movement Report(221023) ⟶ Inventory Name: Armature Winding  |  Company: FAN  |  Date Range: 2026-09-01 to 2026-09-19</t>
+          <t>Production Module ⟶ Advance Production Reports ⟶ Inventory Movement Report(221023) ⟶ Inventory Name: Armature Winding  |  Company: FAN  |  Date Range: 2026-09-01 to 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -639,13 +639,13 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>326,057.91</t>
+          <t>338,176.91</t>
         </is>
       </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>139,823.14</t>
+          <t>132,760.37</t>
         </is>
       </c>
       <c r="I5" s="4" t="n"/>
@@ -1121,19 +1121,19 @@
         <v>11.7339</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>8.629849999999999</v>
+        <v>9.72955</v>
       </c>
       <c r="N7" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O7" s="19" t="n">
-        <v>8.629849999999999</v>
+        <v>9.72955</v>
       </c>
       <c r="P7" s="19" t="n">
-        <v>3.1041</v>
+        <v>2.0044</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>3.10405</v>
+        <v>2.00435</v>
       </c>
       <c r="R7" s="19" t="n">
         <v>0</v>
@@ -1192,19 +1192,19 @@
         <v>7081.106</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>4063.7028</v>
+        <v>4536.0528</v>
       </c>
       <c r="N8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>4063.7028</v>
+        <v>4536.0528</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>3017.4032</v>
+        <v>2545.0532</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>3017.4032</v>
+        <v>2545.0532</v>
       </c>
       <c r="R8" s="16" t="n">
         <v>-0</v>
@@ -1263,22 +1263,22 @@
         <v>10566.05</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>5139.69</v>
+        <v>5738</v>
       </c>
       <c r="N9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>5139.69</v>
+        <v>5738</v>
       </c>
       <c r="P9" s="19" t="n">
-        <v>5426.36</v>
+        <v>4828.05</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>5426.36</v>
+        <v>4828.05</v>
       </c>
       <c r="R9" s="19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" s="18" t="inlineStr"/>
     </row>
@@ -1322,7 +1322,7 @@
         <v>927.5700000000001</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="J10" s="16" t="n">
         <v>0</v>
@@ -1331,22 +1331,22 @@
         <v>0</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1327.57</v>
+        <v>1827.57</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>1244.346</v>
+        <v>1389.2</v>
       </c>
       <c r="N10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1244.346</v>
+        <v>1389.2</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>83.224</v>
+        <v>438.37</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>83.224</v>
+        <v>438.37</v>
       </c>
       <c r="R10" s="16" t="n">
         <v>0</v>
@@ -1405,19 +1405,19 @@
         <v>19554.875</v>
       </c>
       <c r="M11" s="19" t="n">
-        <v>8250.555</v>
+        <v>9211</v>
       </c>
       <c r="N11" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="19" t="n">
-        <v>8250.555</v>
+        <v>9211</v>
       </c>
       <c r="P11" s="19" t="n">
-        <v>11304.32</v>
+        <v>10343.875</v>
       </c>
       <c r="Q11" s="19" t="n">
-        <v>11304.32</v>
+        <v>10343.875</v>
       </c>
       <c r="R11" s="19" t="n">
         <v>0</v>
@@ -1476,19 +1476,19 @@
         <v>20454.875</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>8250.555</v>
+        <v>9211</v>
       </c>
       <c r="N12" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>8250.555</v>
+        <v>9211</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>12204.32</v>
+        <v>11243.875</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>12204.32</v>
+        <v>11243.875</v>
       </c>
       <c r="R12" s="16" t="n">
         <v>0</v>
@@ -1547,19 +1547,19 @@
         <v>19284.875</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>8250.555</v>
+        <v>9211</v>
       </c>
       <c r="N13" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="19" t="n">
-        <v>8250.555</v>
+        <v>9211</v>
       </c>
       <c r="P13" s="19" t="n">
-        <v>11034.32</v>
+        <v>10073.875</v>
       </c>
       <c r="Q13" s="19" t="n">
-        <v>11034.32</v>
+        <v>10073.875</v>
       </c>
       <c r="R13" s="19" t="n">
         <v>0</v>
@@ -1618,19 +1618,19 @@
         <v>203.7185</v>
       </c>
       <c r="M14" s="16" t="n">
-        <v>74.2105</v>
+        <v>80.51049999999999</v>
       </c>
       <c r="N14" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="16" t="n">
-        <v>74.2105</v>
+        <v>80.51049999999999</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>129.508</v>
+        <v>123.208</v>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>129.508</v>
+        <v>123.208</v>
       </c>
       <c r="R14" s="16" t="n">
         <v>-0</v>
@@ -1689,19 +1689,19 @@
         <v>395.04</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>215.575</v>
+        <v>231.775</v>
       </c>
       <c r="N15" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>215.575</v>
+        <v>231.775</v>
       </c>
       <c r="P15" s="19" t="n">
-        <v>179.465</v>
+        <v>163.265</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>179.465</v>
+        <v>163.265</v>
       </c>
       <c r="R15" s="19" t="n">
         <v>0</v>
@@ -1760,19 +1760,19 @@
         <v>81.81399999999999</v>
       </c>
       <c r="M16" s="16" t="n">
-        <v>27.289</v>
+        <v>29.089</v>
       </c>
       <c r="N16" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="16" t="n">
-        <v>27.289</v>
+        <v>29.089</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>54.525</v>
+        <v>52.725</v>
       </c>
       <c r="Q16" s="16" t="n">
-        <v>54.525</v>
+        <v>52.725</v>
       </c>
       <c r="R16" s="16" t="n">
         <v>0</v>
@@ -1831,19 +1831,19 @@
         <v>93957</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>27051</v>
+        <v>30200</v>
       </c>
       <c r="N17" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="19" t="n">
-        <v>27051</v>
+        <v>30200</v>
       </c>
       <c r="P17" s="19" t="n">
-        <v>66906</v>
+        <v>63757</v>
       </c>
       <c r="Q17" s="19" t="n">
-        <v>66906</v>
+        <v>63757</v>
       </c>
       <c r="R17" s="19" t="n">
         <v>0</v>
@@ -1902,19 +1902,19 @@
         <v>54.7385</v>
       </c>
       <c r="M18" s="16" t="n">
-        <v>40.576</v>
+        <v>45.2995</v>
       </c>
       <c r="N18" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="16" t="n">
-        <v>40.576</v>
+        <v>45.2995</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>14.1625</v>
+        <v>9.439</v>
       </c>
       <c r="Q18" s="16" t="n">
-        <v>14.1625</v>
+        <v>9.439</v>
       </c>
       <c r="R18" s="16" t="n">
         <v>0</v>
@@ -1961,7 +1961,7 @@
         <v>238.534</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>375</v>
+        <v>475</v>
       </c>
       <c r="J19" s="19" t="n">
         <v>0</v>
@@ -1970,22 +1970,22 @@
         <v>0</v>
       </c>
       <c r="L19" s="19" t="n">
-        <v>699.17</v>
+        <v>799.17</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>552.634</v>
+        <v>585.034</v>
       </c>
       <c r="N19" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="19" t="n">
-        <v>552.634</v>
+        <v>585.034</v>
       </c>
       <c r="P19" s="19" t="n">
-        <v>146.536</v>
+        <v>214.136</v>
       </c>
       <c r="Q19" s="19" t="n">
-        <v>146.536</v>
+        <v>214.136</v>
       </c>
       <c r="R19" s="19" t="n">
         <v>-0</v>
@@ -2044,19 +2044,19 @@
         <v>5408.66</v>
       </c>
       <c r="M20" s="16" t="n">
-        <v>3259.37</v>
+        <v>3853.37</v>
       </c>
       <c r="N20" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="16" t="n">
-        <v>3259.37</v>
+        <v>3853.37</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>2149.29</v>
+        <v>1555.29</v>
       </c>
       <c r="Q20" s="16" t="n">
-        <v>2149.29</v>
+        <v>1555.29</v>
       </c>
       <c r="R20" s="16" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>234.181</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="J23" s="19" t="n">
         <v>0</v>
@@ -2254,22 +2254,22 @@
         <v>0</v>
       </c>
       <c r="L23" s="19" t="n">
-        <v>716.17</v>
+        <v>836.17</v>
       </c>
       <c r="M23" s="19" t="n">
-        <v>552.634</v>
+        <v>585.034</v>
       </c>
       <c r="N23" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="19" t="n">
-        <v>552.634</v>
+        <v>585.034</v>
       </c>
       <c r="P23" s="19" t="n">
-        <v>163.536</v>
+        <v>251.136</v>
       </c>
       <c r="Q23" s="19" t="n">
-        <v>163.536</v>
+        <v>251.136</v>
       </c>
       <c r="R23" s="19" t="n">
         <v>0</v>
@@ -2390,28 +2390,28 @@
         <v>0</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>15400</v>
+        <v>18400</v>
       </c>
       <c r="K25" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>19735</v>
+        <v>22735</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>19635</v>
+        <v>22735</v>
       </c>
       <c r="N25" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="19" t="n">
-        <v>19635</v>
+        <v>22735</v>
       </c>
       <c r="P25" s="19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R25" s="19" t="n">
         <v>0</v>
@@ -2470,19 +2470,19 @@
         <v>8159</v>
       </c>
       <c r="M26" s="16" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="N26" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="16" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>744</v>
+        <v>695</v>
       </c>
       <c r="Q26" s="16" t="n">
-        <v>744</v>
+        <v>695</v>
       </c>
       <c r="R26" s="16" t="n">
         <v>0</v>
@@ -2603,13 +2603,13 @@
         <v>0</v>
       </c>
       <c r="J28" s="16" t="n">
-        <v>8485</v>
+        <v>9985</v>
       </c>
       <c r="K28" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="16" t="n">
-        <v>16455</v>
+        <v>17955</v>
       </c>
       <c r="M28" s="16" t="n">
         <v>12576</v>
@@ -2621,10 +2621,10 @@
         <v>12576</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>3879</v>
+        <v>5379</v>
       </c>
       <c r="Q28" s="16" t="n">
-        <v>3879</v>
+        <v>5379</v>
       </c>
       <c r="R28" s="16" t="n">
         <v>0</v>
@@ -2745,28 +2745,28 @@
         <v>0</v>
       </c>
       <c r="J30" s="16" t="n">
-        <v>9125</v>
+        <v>11075</v>
       </c>
       <c r="K30" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="16" t="n">
-        <v>9481</v>
+        <v>11431</v>
       </c>
       <c r="M30" s="16" t="n">
-        <v>9339</v>
+        <v>11139</v>
       </c>
       <c r="N30" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="16" t="n">
-        <v>9339</v>
+        <v>11139</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>142</v>
+        <v>292</v>
       </c>
       <c r="Q30" s="16" t="n">
-        <v>142</v>
+        <v>292</v>
       </c>
       <c r="R30" s="16" t="n">
         <v>0</v>
@@ -2961,19 +2961,19 @@
         <v>0</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="M33" s="19" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="P33" s="19" t="n">
         <v>0</v>
@@ -3032,19 +3032,19 @@
         <v>0</v>
       </c>
       <c r="K34" s="16" t="n">
-        <v>10297</v>
+        <v>13397</v>
       </c>
       <c r="L34" s="16" t="n">
-        <v>10297</v>
+        <v>13397</v>
       </c>
       <c r="M34" s="16" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="16" t="n">
-        <v>10297</v>
+        <v>13397</v>
       </c>
       <c r="O34" s="16" t="n">
-        <v>10297</v>
+        <v>13397</v>
       </c>
       <c r="P34" s="16" t="n">
         <v>0</v>
@@ -3251,19 +3251,19 @@
         <v>10589</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="N37" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="P37" s="19" t="n">
-        <v>3174</v>
+        <v>3125</v>
       </c>
       <c r="Q37" s="19" t="n">
-        <v>3174</v>
+        <v>3125</v>
       </c>
       <c r="R37" s="19" t="n">
         <v>0</v>
@@ -3316,25 +3316,25 @@
         <v>0</v>
       </c>
       <c r="K38" s="16" t="n">
-        <v>9339</v>
+        <v>11139</v>
       </c>
       <c r="L38" s="16" t="n">
-        <v>20913</v>
+        <v>22713</v>
       </c>
       <c r="M38" s="16" t="n">
-        <v>10297</v>
+        <v>13397</v>
       </c>
       <c r="N38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="16" t="n">
-        <v>10297</v>
+        <v>13397</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>10616</v>
+        <v>9316</v>
       </c>
       <c r="Q38" s="16" t="n">
-        <v>10616</v>
+        <v>9316</v>
       </c>
       <c r="R38" s="16" t="n">
         <v>0</v>
@@ -3435,15 +3435,15 @@
       <c r="J40" s="20" t="n"/>
       <c r="K40" s="20" t="n"/>
       <c r="L40" s="21" t="n">
-        <v>326057.90545</v>
+        <v>338176.90545</v>
       </c>
       <c r="M40" s="20" t="n"/>
       <c r="N40" s="20" t="n"/>
       <c r="O40" s="21" t="n">
-        <v>186234.7645</v>
+        <v>205416.5367</v>
       </c>
       <c r="P40" s="21" t="n">
-        <v>139823.141</v>
+        <v>132760.3688</v>
       </c>
       <c r="Q40" s="20" t="n"/>
       <c r="R40" s="20" t="n"/>
